--- a/resultados/altopiquiri/inventario_externos.xlsx
+++ b/resultados/altopiquiri/inventario_externos.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:01</t>
+          <t>2026-07-30 15:03:59</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:02</t>
+          <t>2026-07-30 15:04:00</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:02</t>
+          <t>2026-07-30 15:04:00</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:02</t>
+          <t>2026-07-30 15:04:00</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:02</t>
+          <t>2026-07-30 15:04:01</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:02</t>
+          <t>2026-07-30 15:04:01</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:03</t>
+          <t>2026-07-30 15:04:01</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:03</t>
+          <t>2026-07-30 15:04:01</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:03</t>
+          <t>2026-07-30 15:04:02</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:04</t>
+          <t>2026-07-30 15:04:02</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5099,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6029,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6277,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7052,7 +7052,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7331,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8013,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8354,7 +8354,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:05</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:06</t>
+          <t>2026-07-30 15:04:04</t>
         </is>
       </c>
     </row>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9757,7 +9757,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9827,7 +9827,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:07</t>
+          <t>2026-07-30 15:04:05</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:08</t>
+          <t>2026-07-30 15:04:06</t>
         </is>
       </c>
     </row>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:08</t>
+          <t>2026-07-30 15:04:06</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:08</t>
+          <t>2026-07-30 15:04:06</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:08</t>
+          <t>2026-07-30 15:04:06</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:08</t>
+          <t>2026-07-30 15:04:06</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:08</t>
+          <t>2026-07-30 15:04:06</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:08</t>
+          <t>2026-07-30 15:04:06</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10347,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:09</t>
+          <t>2026-07-30 15:04:07</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10661,7 +10661,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10906,7 +10906,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11011,7 +11011,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11151,7 +11151,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11221,7 +11221,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11326,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11536,7 +11536,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11641,7 +11641,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11781,7 +11781,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11851,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11886,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11956,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -11991,7 +11991,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12131,7 +12131,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12201,7 +12201,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12236,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12341,7 +12341,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:10</t>
+          <t>2026-07-30 15:04:08</t>
         </is>
       </c>
     </row>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:11</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12438,7 +12438,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:11</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:11</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12850,7 +12850,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12955,7 +12955,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13130,7 +13130,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13165,7 +13165,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13200,7 +13200,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13270,7 +13270,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13340,7 +13340,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13375,7 +13375,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13620,7 +13620,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13655,7 +13655,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13690,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13760,7 +13760,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13865,7 +13865,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13900,7 +13900,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14005,7 +14005,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14110,7 +14110,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14145,7 +14145,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14180,7 +14180,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14320,7 +14320,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14355,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14460,7 +14460,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14530,7 +14530,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14775,7 +14775,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14880,7 +14880,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14915,7 +14915,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14950,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -14985,7 +14985,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15125,7 +15125,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15335,7 +15335,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15370,7 +15370,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:09</t>
         </is>
       </c>
     </row>
@@ -15432,7 +15432,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15467,7 +15467,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15607,7 +15607,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15642,7 +15642,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15677,7 +15677,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15747,7 +15747,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15852,7 +15852,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15887,7 +15887,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16027,7 +16027,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16202,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16237,7 +16237,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16307,7 +16307,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16412,7 +16412,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16762,7 +16762,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16832,7 +16832,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -16972,7 +16972,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:12</t>
+          <t>2026-07-30 15:04:10</t>
         </is>
       </c>
     </row>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:13</t>
+          <t>2026-07-30 15:04:11</t>
         </is>
       </c>
     </row>
@@ -17135,7 +17135,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:13</t>
+          <t>2026-07-30 15:04:11</t>
         </is>
       </c>
     </row>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:15</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17201,7 +17201,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17232,7 +17232,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17263,7 +17263,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17387,7 +17387,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17635,7 +17635,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17666,7 +17666,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17821,7 +17821,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17852,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17883,7 +17883,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17914,7 +17914,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -17976,7 +17976,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:13</t>
         </is>
       </c>
     </row>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18143,7 +18143,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18213,7 +18213,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18248,7 +18248,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18283,7 +18283,7 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18458,7 +18458,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18493,7 +18493,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18563,7 +18563,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18668,7 +18668,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18703,7 +18703,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18769,7 +18769,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:16</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18800,7 +18800,7 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18835,7 +18835,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18870,7 +18870,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18905,7 +18905,7 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18936,7 +18936,7 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:14</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:15</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19002,7 @@
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:15</t>
         </is>
       </c>
     </row>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:15</t>
         </is>
       </c>
     </row>
@@ -19072,7 +19072,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:15</t>
         </is>
       </c>
     </row>
@@ -19107,7 +19107,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:15</t>
         </is>
       </c>
     </row>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:15</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:15</t>
         </is>
       </c>
     </row>
@@ -19208,7 +19208,7 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:17</t>
+          <t>2026-07-30 15:04:15</t>
         </is>
       </c>
     </row>
@@ -19239,7 +19239,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:20</t>
+          <t>2026-07-30 15:04:18</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:20</t>
+          <t>2026-07-30 15:04:18</t>
         </is>
       </c>
     </row>
@@ -19305,7 +19305,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:22</t>
+          <t>2026-07-30 15:04:19</t>
         </is>
       </c>
     </row>
@@ -19336,7 +19336,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:22</t>
+          <t>2026-07-30 15:04:19</t>
         </is>
       </c>
     </row>
@@ -19371,7 +19371,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:22</t>
+          <t>2026-07-30 15:04:19</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:22</t>
+          <t>2026-07-30 15:04:19</t>
         </is>
       </c>
     </row>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:22</t>
+          <t>2026-07-30 15:04:19</t>
         </is>
       </c>
     </row>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:22</t>
+          <t>2026-07-30 15:04:19</t>
         </is>
       </c>
     </row>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:22</t>
+          <t>2026-07-30 15:04:19</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:22</t>
+          <t>2026-07-30 15:04:19</t>
         </is>
       </c>
     </row>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19604,7 +19604,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19635,7 +19635,7 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19697,7 +19697,7 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19728,7 +19728,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19790,7 +19790,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19852,7 +19852,7 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:20</t>
         </is>
       </c>
     </row>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:21</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:21</t>
         </is>
       </c>
     </row>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:23</t>
+          <t>2026-07-30 15:04:21</t>
         </is>
       </c>
     </row>
@@ -19980,7 +19980,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:24</t>
+          <t>2026-07-30 15:04:21</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:24</t>
+          <t>2026-07-30 15:04:21</t>
         </is>
       </c>
     </row>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:25</t>
+          <t>2026-07-30 15:04:22</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:25</t>
+          <t>2026-07-30 15:04:22</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:25</t>
+          <t>2026-07-30 15:04:22</t>
         </is>
       </c>
     </row>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:25</t>
+          <t>2026-07-30 15:04:22</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:26</t>
+          <t>2026-07-30 15:04:23</t>
         </is>
       </c>
     </row>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:26</t>
+          <t>2026-07-30 15:04:23</t>
         </is>
       </c>
     </row>
@@ -20232,7 +20232,7 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:26</t>
+          <t>2026-07-30 15:04:23</t>
         </is>
       </c>
     </row>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:26</t>
+          <t>2026-07-30 15:04:23</t>
         </is>
       </c>
     </row>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:26</t>
+          <t>2026-07-30 15:04:23</t>
         </is>
       </c>
     </row>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20356,7 +20356,7 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20387,7 +20387,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20418,7 +20418,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20449,7 +20449,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20480,7 +20480,7 @@
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20573,7 +20573,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20728,7 +20728,7 @@
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20759,7 +20759,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20790,7 +20790,7 @@
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20821,7 +20821,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20852,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20914,7 +20914,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20945,7 +20945,7 @@
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -20976,7 +20976,7 @@
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21069,7 +21069,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21100,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21162,7 +21162,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21193,7 +21193,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21255,7 +21255,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21286,7 +21286,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21379,7 +21379,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21472,7 +21472,7 @@
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21503,7 +21503,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21534,7 +21534,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21658,7 +21658,7 @@
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21720,7 +21720,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21751,7 +21751,7 @@
       </c>
       <c r="G655" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21813,7 +21813,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21844,7 +21844,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21906,7 +21906,7 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21937,7 +21937,7 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21968,7 +21968,7 @@
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -21999,7 +21999,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22030,7 +22030,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22123,7 +22123,7 @@
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22185,7 +22185,7 @@
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22216,7 +22216,7 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22247,7 +22247,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:28</t>
+          <t>2026-07-30 15:04:25</t>
         </is>
       </c>
     </row>
@@ -22309,7 +22309,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22340,7 +22340,7 @@
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22433,7 +22433,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22464,7 +22464,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22495,7 +22495,7 @@
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22526,7 +22526,7 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22557,7 +22557,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22588,7 +22588,7 @@
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22619,7 +22619,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22650,7 +22650,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22681,7 +22681,7 @@
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22712,7 +22712,7 @@
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22774,7 +22774,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22805,7 +22805,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22836,7 +22836,7 @@
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22898,7 +22898,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22929,7 +22929,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22960,7 +22960,7 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -22991,7 +22991,7 @@
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -23022,7 +23022,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -23084,7 +23084,7 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -23115,7 +23115,7 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:29</t>
+          <t>2026-07-30 15:04:26</t>
         </is>
       </c>
     </row>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:32</t>
+          <t>2026-07-30 15:04:29</t>
         </is>
       </c>
     </row>
@@ -23239,7 +23239,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:33</t>
+          <t>2026-07-30 15:04:29</t>
         </is>
       </c>
     </row>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:33</t>
+          <t>2026-07-30 15:04:29</t>
         </is>
       </c>
     </row>
@@ -23301,7 +23301,7 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23336,7 +23336,7 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23371,7 +23371,7 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23406,7 +23406,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23441,7 +23441,7 @@
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23476,7 +23476,7 @@
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23511,7 +23511,7 @@
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23546,7 +23546,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23581,7 +23581,7 @@
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23616,7 +23616,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:34</t>
+          <t>2026-07-30 15:04:30</t>
         </is>
       </c>
     </row>
@@ -23678,7 +23678,7 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:35</t>
+          <t>2026-07-30 15:04:31</t>
         </is>
       </c>
     </row>
@@ -23713,7 +23713,7 @@
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:35</t>
+          <t>2026-07-30 15:04:31</t>
         </is>
       </c>
     </row>
@@ -23744,7 +23744,7 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:35</t>
+          <t>2026-07-30 15:04:31</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -23810,7 +23810,7 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -23845,7 +23845,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23880,7 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -23915,7 +23915,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -23950,7 +23950,7 @@
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -23985,7 +23985,7 @@
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -24051,7 +24051,7 @@
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:38</t>
         </is>
       </c>
     </row>
@@ -24082,7 +24082,7 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:39</t>
         </is>
       </c>
     </row>
@@ -24117,7 +24117,7 @@
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:39</t>
         </is>
       </c>
     </row>
@@ -24152,7 +24152,7 @@
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:39</t>
         </is>
       </c>
     </row>
@@ -24183,7 +24183,7 @@
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:42</t>
+          <t>2026-07-30 15:04:39</t>
         </is>
       </c>
     </row>
@@ -24214,7 +24214,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:51</t>
+          <t>2026-07-30 15:04:48</t>
         </is>
       </c>
     </row>
@@ -24249,7 +24249,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:51</t>
+          <t>2026-07-30 15:04:48</t>
         </is>
       </c>
     </row>
@@ -24280,7 +24280,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:51</t>
+          <t>2026-07-30 15:04:48</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:52</t>
+          <t>2026-07-30 15:04:48</t>
         </is>
       </c>
     </row>
@@ -24342,7 +24342,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:52</t>
+          <t>2026-07-30 15:04:48</t>
         </is>
       </c>
     </row>
@@ -24377,7 +24377,7 @@
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:56</t>
+          <t>2026-07-30 15:04:53</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:57</t>
+          <t>2026-07-30 15:04:54</t>
         </is>
       </c>
     </row>
@@ -24439,7 +24439,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:57</t>
+          <t>2026-07-30 15:04:54</t>
         </is>
       </c>
     </row>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:58</t>
+          <t>2026-07-30 15:04:54</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:58</t>
+          <t>2026-07-30 15:04:54</t>
         </is>
       </c>
     </row>
@@ -24532,7 +24532,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:59</t>
+          <t>2026-07-30 15:04:55</t>
         </is>
       </c>
     </row>
@@ -24567,7 +24567,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:59</t>
+          <t>2026-07-30 15:04:55</t>
         </is>
       </c>
     </row>
@@ -24598,7 +24598,7 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:59</t>
+          <t>2026-07-30 15:04:55</t>
         </is>
       </c>
     </row>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:59</t>
+          <t>2026-07-30 15:04:55</t>
         </is>
       </c>
     </row>
@@ -24664,7 +24664,7 @@
       </c>
       <c r="G746" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:59</t>
+          <t>2026-07-30 15:04:55</t>
         </is>
       </c>
     </row>
@@ -24695,7 +24695,7 @@
       </c>
       <c r="G747" t="inlineStr">
         <is>
-          <t>2026-07-29 13:29:59</t>
+          <t>2026-07-30 15:04:55</t>
         </is>
       </c>
     </row>
